--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.67026194531058</v>
+        <v>9.533917566112969</v>
       </c>
       <c r="D2" t="n">
-        <v>58.46575268334472</v>
+        <v>9.500684811043516</v>
       </c>
       <c r="E2" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F2" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.15517276988967</v>
+        <v>5.875215575107071</v>
       </c>
       <c r="D3" t="n">
-        <v>21.3134373258091</v>
+        <v>3.463433565443979</v>
       </c>
       <c r="E3" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F3" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09258238107306</v>
+        <v>4.890044636924373</v>
       </c>
       <c r="D4" t="n">
-        <v>17.40406174243378</v>
+        <v>2.828160033145489</v>
       </c>
       <c r="E4" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F4" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.46641673440051</v>
+        <v>3.000792719340083</v>
       </c>
       <c r="D5" t="n">
-        <v>22.21527016758339</v>
+        <v>3.609981402232301</v>
       </c>
       <c r="E5" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F5" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.55943876110157</v>
+        <v>7.403408798679006</v>
       </c>
       <c r="D6" t="n">
-        <v>30.40278028584286</v>
+        <v>4.940451796449465</v>
       </c>
       <c r="E6" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F6" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.22694595998102</v>
+        <v>2.961878718496916</v>
       </c>
       <c r="D7" t="n">
-        <v>18.2553550560993</v>
+        <v>2.966495196616136</v>
       </c>
       <c r="E7" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F7" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.28000229402544</v>
+        <v>5.895500372779134</v>
       </c>
       <c r="D8" t="n">
-        <v>36.56236482791928</v>
+        <v>5.941384284536883</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F8" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.35326815220248</v>
+        <v>1.519906074732903</v>
       </c>
       <c r="D9" t="n">
-        <v>9.403630989407612</v>
+        <v>1.528090035778737</v>
       </c>
       <c r="E9" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F9" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.49110120382738</v>
+        <v>9.017303945621949</v>
       </c>
       <c r="D10" t="n">
-        <v>16.01315490215208</v>
+        <v>2.602137671599714</v>
       </c>
       <c r="E10" t="n">
-        <v>16.07682418901869</v>
+        <v>2.612483930715537</v>
       </c>
       <c r="F10" t="n">
-        <v>13.85865674167667</v>
+        <v>2.252031720522459</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
